--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -458,7 +458,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -577,7 +577,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>ඔයාගෙ අම්මගෙන් අනුමැතිය ගත්තද?</t>
+          <t>ඔයාගෙ අම්මගෙන් අනුමතිය ගත්තද?</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
